--- a/03_Outputs/all/01_TablasDescriptivas/idx13_saludmental.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx13_saludmental.xlsx
@@ -440,7 +440,7 @@
         <v>125</v>
       </c>
       <c r="C4">
-        <v>-85.71146515508923</v>
+        <v>-85.71146515508924</v>
       </c>
       <c r="D4">
         <v>47.27665218376739</v>
@@ -465,7 +465,7 @@
         <v>-174.3586572892585</v>
       </c>
       <c r="D5">
-        <v>95.01969049143014</v>
+        <v>95.01969049143013</v>
       </c>
       <c r="E5">
         <v>-494.077028394547</v>
@@ -484,10 +484,10 @@
         <v>125</v>
       </c>
       <c r="C6">
-        <v>-49.48237287474198</v>
+        <v>-49.48237287474197</v>
       </c>
       <c r="D6">
-        <v>30.90493490908363</v>
+        <v>30.90493490908362</v>
       </c>
       <c r="E6">
         <v>-174.135128859995</v>
@@ -597,7 +597,7 @@
         <v>-18.09863262024607</v>
       </c>
       <c r="D11">
-        <v>22.68887587369681</v>
+        <v>22.68887587369682</v>
       </c>
       <c r="E11">
         <v>-149.700598802395</v>
@@ -619,7 +619,7 @@
         <v>-11.82448105393056</v>
       </c>
       <c r="D12">
-        <v>14.78206809686439</v>
+        <v>14.7820680968644</v>
       </c>
       <c r="E12">
         <v>-93.0521091811414</v>
